--- a/output/pdf_financials_xlsx/JTC.xlsx
+++ b/output/pdf_financials_xlsx/JTC.xlsx
@@ -5987,16 +5987,16 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.306348</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.337113</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.337113</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.337113</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -19464,7 +19464,11 @@
           <t>Share-based payments reserve 8</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -19971,7 +19975,11 @@
           <t>Share-based payments reserve 4,9</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -37819,7 +37827,7 @@
         <v>-0.14937</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.034024</v>
+        <v>-0.034024</v>
       </c>
       <c r="N302" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/JTC.xlsx
+++ b/output/pdf_financials_xlsx/JTC.xlsx
@@ -1029,55 +1029,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.044654</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.015464</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.036542</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.033564</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.0365</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.036743</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.019528</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.009686999999999999</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.011735</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.019198</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.018516</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.003105</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.00554</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.036157</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.056331</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.05485</v>
       </c>
     </row>
     <row r="13">
@@ -1954,28 +1954,20 @@
       <c r="C26" s="3" t="n">
         <v>-1.09763</v>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D26" s="3" t="n">
+        <v>2.395654</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>2.395654</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2.395654</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>2.395654</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>2.44347</v>
+        <v>2.481216</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>2.485654</v>
@@ -2015,10 +2007,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.163535</v>
+        <v>0.118881</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.246914</v>
+        <v>-0.262378</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2041,37 +2033,37 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.244347</v>
+        <v>-0.263875</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.14937</v>
+        <v>-0.159057</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.034024</v>
+        <v>0.025124</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.234691</v>
+        <v>0.222956</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.55821</v>
+        <v>0.539012</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.57873</v>
+        <v>0.560214</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.67661</v>
+        <v>0.673505</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.780957</v>
+        <v>0.775417</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.221906</v>
+        <v>-0.258063</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.118835</v>
+        <v>0.062504</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.187711</v>
+        <v>0.132861</v>
       </c>
     </row>
     <row r="28">
@@ -2139,10 +2131,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.163535</v>
+        <v>0.118881</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.246914</v>
+        <v>-0.262378</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2165,37 +2157,37 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.180375</v>
+        <v>-0.199903</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.130291</v>
+        <v>-0.139978</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.034529</v>
+        <v>0.025629</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.318597</v>
+        <v>0.306862</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.669916</v>
+        <v>0.650718</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.6728499999999999</v>
+        <v>0.654334</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.705238</v>
+        <v>0.702133</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.814843</v>
+        <v>0.809303</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.162637</v>
+        <v>-0.198794</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.208278</v>
+        <v>0.151947</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.278446</v>
+        <v>0.223596</v>
       </c>
     </row>
     <row r="30">
@@ -2205,10 +2197,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>8.938859263049034</v>
+        <v>6.498061748558611</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-22.837370882292</v>
+        <v>-24.26765471927073</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2231,37 +2223,37 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-24.94937507261772</v>
+        <v>-27.65047775546224</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-14.32072956132454</v>
+        <v>-15.38546087247076</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.831527051583995</v>
+        <v>2.101688632889635</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>17.20455249921969</v>
+        <v>16.57085091515473</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>28.74921788030758</v>
+        <v>27.92534222296226</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>28.42412846683753</v>
+        <v>27.64193159875109</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>27.47355831973104</v>
+        <v>27.35259858899792</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>28.99795089113816</v>
+        <v>28.80079800654946</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-11.2554205427671</v>
+        <v>-13.75769395266048</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>12.30917434716957</v>
+        <v>8.980027244977261</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>15.01196607554235</v>
+        <v>12.05481697214888</v>
       </c>
     </row>
     <row r="31">
@@ -2457,10 +2449,10 @@
         <v>2.131728</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.406673</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.50806</v>
       </c>
     </row>
     <row r="35">
@@ -2577,10 +2569,10 @@
         <v>2.131728</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>2.406673</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2.50806</v>
       </c>
     </row>
     <row r="37">
@@ -3297,10 +3289,10 @@
         <v>0.103358</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.432436</v>
+        <v>0.025763</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.535971</v>
+        <v>0.027911</v>
       </c>
     </row>
     <row r="49">
@@ -7862,22 +7854,22 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.010641</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.029117</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.029568</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.05443</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.09882199999999999</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.100532</v>
       </c>
     </row>
     <row r="125">
@@ -7920,22 +7912,22 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.010641</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.029117</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.029568</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.05443</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.09882199999999999</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.100532</v>
       </c>
     </row>
     <row r="126">
@@ -8735,7 +8727,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -21453,7 +21445,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -24228,7 +24224,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -35667,7 +35667,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E280" s="5" t="n">
@@ -38193,7 +38193,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
